--- a/four_boiling.xlsx
+++ b/four_boiling.xlsx
@@ -588,10 +588,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I261"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -5613,6 +5613,14 @@
           <t>°F</t>
         </is>
       </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="17" t="inlineStr">
+        <is>
+          <t>Note: if using CoolingTowerSystem, ignore these injection water demands - they are re-solved there at the delivered water temp.</t>
+        </is>
+      </c>
+      <c r="B262" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="21">

--- a/four_boiling.xlsx
+++ b/four_boiling.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -176,6 +176,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -588,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:I277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -2113,1958 +2116,1860 @@
       <c r="H122" s="15" t="inlineStr"/>
       <c r="I122" s="15" t="inlineStr"/>
     </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B124" s="21" t="n">
+        <v>21.696</v>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B125" s="22" t="n">
+        <v>27840.69215811958</v>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="17" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>A1 CENTRIFUGALS  [A1 Centrifugals]</t>
         </is>
       </c>
-      <c r="B124" s="5" t="n"/>
-      <c r="C124" s="5" t="n"/>
-      <c r="D124" s="5" t="n"/>
-      <c r="E124" s="5" t="n"/>
-      <c r="F124" s="5" t="n"/>
-      <c r="G124" s="5" t="n"/>
-      <c r="H124" s="5" t="n"/>
-      <c r="I124" s="5" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
+      <c r="I127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G125" s="6" t="inlineStr">
+      <c r="G128" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
+      <c r="I128" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C126" s="9" t="n">
+      <c r="C129" s="9" t="n">
         <v>67463.72353255494</v>
       </c>
-      <c r="D126" s="9" t="n">
+      <c r="D129" s="9" t="n">
         <v>62066.62564995054</v>
       </c>
-      <c r="E126" s="9" t="n">
+      <c r="E129" s="9" t="n">
         <v>55455.12587094953</v>
       </c>
-      <c r="F126" s="9" t="n">
+      <c r="F129" s="9" t="n">
         <v>5397.097882604401</v>
       </c>
-      <c r="G126" s="10" t="n">
+      <c r="G129" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H126" s="10" t="n">
+      <c r="H129" s="10" t="n">
         <v>89.34773767742878</v>
       </c>
-      <c r="I126" s="9" t="n">
+      <c r="I129" s="9" t="n">
         <v>723.7952964176816</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="12" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B127" s="12" t="inlineStr">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C127" s="13" t="n">
+      <c r="C130" s="13" t="n">
         <v>385.4028910540364</v>
       </c>
-      <c r="D127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="13" t="n">
+      <c r="D130" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="13" t="n">
         <v>385.4028910540364</v>
       </c>
-      <c r="G127" s="12" t="inlineStr"/>
-      <c r="H127" s="12" t="inlineStr"/>
-      <c r="I127" s="12" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="G130" s="12" t="inlineStr"/>
+      <c r="H130" s="12" t="inlineStr"/>
+      <c r="I130" s="12" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C128" s="9" t="n">
+      <c r="C131" s="9" t="n">
         <v>36125.51675613019</v>
       </c>
-      <c r="D128" s="9" t="n">
+      <c r="D131" s="9" t="n">
         <v>36053.26572261793</v>
       </c>
-      <c r="E128" s="9" t="n">
+      <c r="E131" s="9" t="n">
         <v>35945.10592545007</v>
       </c>
-      <c r="F128" s="9" t="n">
+      <c r="F131" s="9" t="n">
         <v>72.25103351225698</v>
       </c>
-      <c r="G128" s="10" t="n">
+      <c r="G131" s="10" t="n">
         <v>99.8</v>
       </c>
-      <c r="H128" s="10" t="n">
+      <c r="H131" s="10" t="n">
         <v>99.7</v>
       </c>
-      <c r="I128" s="9" t="n">
+      <c r="I131" s="9" t="n">
         <v>373.4870846426217</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="12" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C129" s="13" t="n">
+      <c r="C132" s="13" t="n">
         <v>31723.6096674788</v>
       </c>
-      <c r="D129" s="13" t="n">
+      <c r="D132" s="13" t="n">
         <v>26013.35992733261</v>
       </c>
-      <c r="E129" s="13" t="n">
+      <c r="E132" s="13" t="n">
         <v>19510.01994549946</v>
       </c>
-      <c r="F129" s="13" t="n">
+      <c r="F132" s="13" t="n">
         <v>5710.249740146184</v>
       </c>
-      <c r="G129" s="14" t="n">
+      <c r="G132" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H129" s="14" t="n">
+      <c r="H132" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="I129" s="13" t="n">
+      <c r="I132" s="13" t="n">
         <v>356.8484510754353</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="15" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B130" s="15" t="inlineStr"/>
-      <c r="C130" s="16" t="n">
+      <c r="B133" s="15" t="inlineStr"/>
+      <c r="C133" s="16" t="n">
         <v>67849.12642360898</v>
       </c>
-      <c r="D130" s="16" t="n">
+      <c r="D133" s="16" t="n">
         <v>62066.62564995054</v>
       </c>
-      <c r="E130" s="16" t="n">
+      <c r="E133" s="16" t="n">
         <v>55455.12587094953</v>
       </c>
-      <c r="F130" s="16" t="n">
+      <c r="F133" s="16" t="n">
         <v>5782.500773658438</v>
       </c>
-      <c r="G130" s="15" t="inlineStr"/>
-      <c r="H130" s="15" t="inlineStr"/>
-      <c r="I130" s="15" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="15" t="inlineStr">
+      <c r="G133" s="15" t="inlineStr"/>
+      <c r="H133" s="15" t="inlineStr"/>
+      <c r="I133" s="15" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B131" s="15" t="inlineStr"/>
-      <c r="C131" s="16" t="n">
+      <c r="B134" s="15" t="inlineStr"/>
+      <c r="C134" s="16" t="n">
         <v>67849.12642360898</v>
       </c>
-      <c r="D131" s="16" t="n">
+      <c r="D134" s="16" t="n">
         <v>62066.62564995054</v>
       </c>
-      <c r="E131" s="16" t="n">
+      <c r="E134" s="16" t="n">
         <v>55455.12587094953</v>
       </c>
-      <c r="F131" s="16" t="n">
+      <c r="F134" s="16" t="n">
         <v>5782.500773658438</v>
       </c>
-      <c r="G131" s="15" t="inlineStr"/>
-      <c r="H131" s="15" t="inlineStr"/>
-      <c r="I131" s="15" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="15" t="inlineStr">
+      <c r="G134" s="15" t="inlineStr"/>
+      <c r="H134" s="15" t="inlineStr"/>
+      <c r="I134" s="15" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B132" s="15" t="inlineStr"/>
-      <c r="C132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="15" t="inlineStr"/>
-      <c r="H132" s="15" t="inlineStr"/>
-      <c r="I132" s="15" t="inlineStr"/>
-    </row>
-    <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="B135" s="15" t="inlineStr"/>
+      <c r="C135" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="15" t="inlineStr"/>
+      <c r="H135" s="15" t="inlineStr"/>
+      <c r="I135" s="15" t="inlineStr"/>
+    </row>
+    <row r="137" ht="17" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>A1 MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
-      <c r="B134" s="5" t="n"/>
-      <c r="C134" s="5" t="n"/>
-      <c r="D134" s="5" t="n"/>
-      <c r="E134" s="5" t="n"/>
-      <c r="F134" s="5" t="n"/>
-      <c r="G134" s="5" t="n"/>
-      <c r="H134" s="5" t="n"/>
-      <c r="I134" s="5" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+      <c r="B137" s="5" t="n"/>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
+      <c r="E137" s="5" t="n"/>
+      <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
+      <c r="H137" s="5" t="n"/>
+      <c r="I137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G135" s="6" t="inlineStr">
+      <c r="G138" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H138" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>A1 Molasses (undiluted)</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C136" s="9" t="n">
+      <c r="C139" s="9" t="n">
         <v>31723.6096674788</v>
       </c>
-      <c r="D136" s="9" t="n">
+      <c r="D139" s="9" t="n">
         <v>26013.35992733261</v>
       </c>
-      <c r="E136" s="9" t="n">
+      <c r="E139" s="9" t="n">
         <v>19510.01994549946</v>
       </c>
-      <c r="F136" s="9" t="n">
+      <c r="F139" s="9" t="n">
         <v>5710.249740146184</v>
       </c>
-      <c r="G136" s="10" t="n">
+      <c r="G139" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H136" s="10" t="n">
+      <c r="H139" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="I136" s="9" t="n">
+      <c r="I139" s="9" t="n">
         <v>356.8484510754353</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="12" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
         <is>
           <t>Dilution Water</t>
         </is>
       </c>
-      <c r="B137" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C137" s="13" t="n">
+      <c r="C140" s="13" t="n">
         <v>5438.333085853508</v>
       </c>
-      <c r="D137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" s="13" t="n">
+      <c r="D140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="13" t="n">
         <v>5438.333085853508</v>
       </c>
-      <c r="G137" s="12" t="inlineStr"/>
-      <c r="H137" s="12" t="inlineStr"/>
-      <c r="I137" s="12" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="G140" s="12" t="inlineStr"/>
+      <c r="H140" s="12" t="inlineStr"/>
+      <c r="I140" s="12" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>A1 Molasses (diluted)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C138" s="9" t="n">
+      <c r="C141" s="9" t="n">
         <v>37161.9427533323</v>
       </c>
-      <c r="D138" s="9" t="n">
+      <c r="D141" s="9" t="n">
         <v>26013.35992733261</v>
       </c>
-      <c r="E138" s="9" t="n">
+      <c r="E141" s="9" t="n">
         <v>19510.01994549946</v>
       </c>
-      <c r="F138" s="9" t="n">
+      <c r="F141" s="9" t="n">
         <v>11148.58282599969</v>
       </c>
-      <c r="G138" s="10" t="n">
+      <c r="G141" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H138" s="10" t="n">
+      <c r="H141" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="I138" s="9" t="n">
+      <c r="I141" s="9" t="n">
         <v>442.2132541080713</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="15" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B139" s="15" t="inlineStr"/>
-      <c r="C139" s="16" t="n">
+      <c r="B142" s="15" t="inlineStr"/>
+      <c r="C142" s="16" t="n">
         <v>37161.9427533323</v>
       </c>
-      <c r="D139" s="16" t="n">
+      <c r="D142" s="16" t="n">
         <v>26013.35992733261</v>
       </c>
-      <c r="E139" s="16" t="n">
+      <c r="E142" s="16" t="n">
         <v>19510.01994549946</v>
       </c>
-      <c r="F139" s="16" t="n">
+      <c r="F142" s="16" t="n">
         <v>11148.58282599969</v>
       </c>
-      <c r="G139" s="15" t="inlineStr"/>
-      <c r="H139" s="15" t="inlineStr"/>
-      <c r="I139" s="15" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="inlineStr">
+      <c r="G142" s="15" t="inlineStr"/>
+      <c r="H142" s="15" t="inlineStr"/>
+      <c r="I142" s="15" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B140" s="15" t="inlineStr"/>
-      <c r="C140" s="16" t="n">
+      <c r="B143" s="15" t="inlineStr"/>
+      <c r="C143" s="16" t="n">
         <v>37161.9427533323</v>
       </c>
-      <c r="D140" s="16" t="n">
+      <c r="D143" s="16" t="n">
         <v>26013.35992733261</v>
       </c>
-      <c r="E140" s="16" t="n">
+      <c r="E143" s="16" t="n">
         <v>19510.01994549946</v>
       </c>
-      <c r="F140" s="16" t="n">
+      <c r="F143" s="16" t="n">
         <v>11148.58282599969</v>
       </c>
-      <c r="G140" s="15" t="inlineStr"/>
-      <c r="H140" s="15" t="inlineStr"/>
-      <c r="I140" s="15" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="inlineStr">
+      <c r="G143" s="15" t="inlineStr"/>
+      <c r="H143" s="15" t="inlineStr"/>
+      <c r="I143" s="15" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B141" s="15" t="inlineStr"/>
-      <c r="C141" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" s="15" t="inlineStr"/>
-      <c r="H141" s="15" t="inlineStr"/>
-      <c r="I141" s="15" t="inlineStr"/>
-    </row>
-    <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="B144" s="15" t="inlineStr"/>
+      <c r="C144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="15" t="inlineStr"/>
+      <c r="H144" s="15" t="inlineStr"/>
+      <c r="I144" s="15" t="inlineStr"/>
+    </row>
+    <row r="146" ht="17" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>A2 PANS  [A2 Pans]</t>
         </is>
       </c>
-      <c r="B143" s="5" t="n"/>
-      <c r="C143" s="5" t="n"/>
-      <c r="D143" s="5" t="n"/>
-      <c r="E143" s="5" t="n"/>
-      <c r="F143" s="5" t="n"/>
-      <c r="G143" s="5" t="n"/>
-      <c r="H143" s="5" t="n"/>
-      <c r="I143" s="5" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+      <c r="E146" s="5" t="n"/>
+      <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5" t="n"/>
+      <c r="H146" s="5" t="n"/>
+      <c r="I146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G144" s="6" t="inlineStr">
+      <c r="G147" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H144" s="6" t="inlineStr">
+      <c r="H147" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I144" s="6" t="inlineStr">
+      <c r="I147" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>Syrup</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C145" s="9" t="n">
+      <c r="C148" s="9" t="n">
         <v>22037.98433977616</v>
       </c>
-      <c r="D145" s="9" t="n">
+      <c r="D148" s="9" t="n">
         <v>14324.68982085451</v>
       </c>
-      <c r="E145" s="9" t="n">
+      <c r="E148" s="9" t="n">
         <v>12739.73604131815</v>
       </c>
-      <c r="F145" s="9" t="n">
+      <c r="F148" s="9" t="n">
         <v>7713.294518921655</v>
       </c>
-      <c r="G145" s="10" t="n">
+      <c r="G148" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="H145" s="10" t="n">
+      <c r="H148" s="10" t="n">
         <v>88.93551065078627</v>
       </c>
-      <c r="I145" s="9" t="n">
+      <c r="I148" s="9" t="n">
         <v>268.3926598505707</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="12" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
         <is>
           <t>A1 Molasses</t>
         </is>
       </c>
-      <c r="B146" s="12" t="inlineStr">
+      <c r="B149" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C146" s="13" t="n">
+      <c r="C149" s="13" t="n">
         <v>29729.55420266584</v>
       </c>
-      <c r="D146" s="13" t="n">
+      <c r="D149" s="13" t="n">
         <v>20810.68794186609</v>
       </c>
-      <c r="E146" s="13" t="n">
+      <c r="E149" s="13" t="n">
         <v>15608.01595639957</v>
       </c>
-      <c r="F146" s="13" t="n">
+      <c r="F149" s="13" t="n">
         <v>8918.866260799754</v>
       </c>
-      <c r="G146" s="14" t="n">
+      <c r="G149" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H146" s="14" t="n">
+      <c r="H149" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="I146" s="13" t="n">
+      <c r="I149" s="13" t="n">
         <v>353.7706032864571</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="8" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>B Magma</t>
         </is>
       </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="B150" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C147" s="9" t="n">
+      <c r="C150" s="9" t="n">
         <v>9075.042197550176</v>
       </c>
-      <c r="D147" s="9" t="n">
+      <c r="D150" s="9" t="n">
         <v>8349.038821746162</v>
       </c>
-      <c r="E147" s="9" t="n">
+      <c r="E150" s="9" t="n">
         <v>7681.115716006469</v>
       </c>
-      <c r="F147" s="9" t="n">
+      <c r="F150" s="9" t="n">
         <v>726.0033758040136</v>
       </c>
-      <c r="G147" s="10" t="n">
+      <c r="G150" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H147" s="10" t="n">
+      <c r="H150" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I147" s="9" t="n">
+      <c r="I150" s="9" t="n">
         <v>97.36303473094173</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="12" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B148" s="12" t="inlineStr">
+      <c r="B151" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C148" s="13" t="n">
+      <c r="C151" s="13" t="n">
         <v>47265.67020050735</v>
       </c>
-      <c r="D148" s="13" t="n">
+      <c r="D151" s="13" t="n">
         <v>43484.41658446676</v>
       </c>
-      <c r="E148" s="13" t="n">
+      <c r="E151" s="13" t="n">
         <v>36028.86771372419</v>
       </c>
-      <c r="F148" s="13" t="n">
+      <c r="F151" s="13" t="n">
         <v>3781.253616040587</v>
       </c>
-      <c r="G148" s="14" t="n">
+      <c r="G151" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="H148" s="14" t="n">
+      <c r="H151" s="14" t="n">
         <v>82.85466505854929</v>
       </c>
-      <c r="I148" s="13" t="n">
+      <c r="I151" s="13" t="n">
         <v>507.097266231504</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C149" s="9" t="n">
+      <c r="C152" s="9" t="n">
         <v>13576.91053948484</v>
       </c>
-      <c r="D149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="9" t="n">
+      <c r="D152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="9" t="n">
         <v>13576.91053948484</v>
       </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="8" t="inlineStr"/>
-      <c r="I149" s="8" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="inlineStr">
+      <c r="G152" s="8" t="inlineStr"/>
+      <c r="H152" s="8" t="inlineStr"/>
+      <c r="I152" s="8" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B150" s="15" t="inlineStr"/>
-      <c r="C150" s="16" t="n">
+      <c r="B153" s="15" t="inlineStr"/>
+      <c r="C153" s="16" t="n">
         <v>60842.58073999218</v>
       </c>
-      <c r="D150" s="16" t="n">
+      <c r="D153" s="16" t="n">
         <v>43484.41658446676</v>
       </c>
-      <c r="E150" s="16" t="n">
+      <c r="E153" s="16" t="n">
         <v>36028.86771372419</v>
       </c>
-      <c r="F150" s="16" t="n">
+      <c r="F153" s="16" t="n">
         <v>17358.16415552542</v>
       </c>
-      <c r="G150" s="15" t="inlineStr"/>
-      <c r="H150" s="15" t="inlineStr"/>
-      <c r="I150" s="15" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="15" t="inlineStr">
+      <c r="G153" s="15" t="inlineStr"/>
+      <c r="H153" s="15" t="inlineStr"/>
+      <c r="I153" s="15" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B151" s="15" t="inlineStr"/>
-      <c r="C151" s="16" t="n">
+      <c r="B154" s="15" t="inlineStr"/>
+      <c r="C154" s="16" t="n">
         <v>60842.58073999218</v>
       </c>
-      <c r="D151" s="16" t="n">
+      <c r="D154" s="16" t="n">
         <v>43484.41658446676</v>
       </c>
-      <c r="E151" s="16" t="n">
+      <c r="E154" s="16" t="n">
         <v>36028.86771372419</v>
       </c>
-      <c r="F151" s="16" t="n">
+      <c r="F154" s="16" t="n">
         <v>17358.16415552542</v>
       </c>
-      <c r="G151" s="15" t="inlineStr"/>
-      <c r="H151" s="15" t="inlineStr"/>
-      <c r="I151" s="15" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="15" t="inlineStr">
+      <c r="G154" s="15" t="inlineStr"/>
+      <c r="H154" s="15" t="inlineStr"/>
+      <c r="I154" s="15" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B152" s="15" t="inlineStr"/>
-      <c r="C152" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" s="15" t="inlineStr"/>
-      <c r="H152" s="15" t="inlineStr"/>
-      <c r="I152" s="15" t="inlineStr"/>
-    </row>
-    <row r="154" ht="17" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
+      <c r="B155" s="15" t="inlineStr"/>
+      <c r="C155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="15" t="inlineStr"/>
+      <c r="H155" s="15" t="inlineStr"/>
+      <c r="I155" s="15" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B157" s="21" t="n">
+        <v>21.696</v>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="n">
+        <v>15716.26931938715</v>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="17" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>A2 CENTRIFUGALS  [A2 Centrifugals]</t>
         </is>
       </c>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="n"/>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="5" t="n"/>
-      <c r="H154" s="5" t="n"/>
-      <c r="I154" s="5" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="6" t="inlineStr">
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
+      <c r="H160" s="5" t="n"/>
+      <c r="I160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="B161" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
+      <c r="C161" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D161" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E161" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G155" s="6" t="inlineStr">
+      <c r="G161" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H155" s="6" t="inlineStr">
+      <c r="H161" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I155" s="6" t="inlineStr">
+      <c r="I161" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B162" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C156" s="9" t="n">
+      <c r="C162" s="9" t="n">
         <v>47265.67020050735</v>
       </c>
-      <c r="D156" s="9" t="n">
+      <c r="D162" s="9" t="n">
         <v>43484.41658446676</v>
       </c>
-      <c r="E156" s="9" t="n">
+      <c r="E162" s="9" t="n">
         <v>36028.86771372419</v>
       </c>
-      <c r="F156" s="9" t="n">
+      <c r="F162" s="9" t="n">
         <v>3781.253616040587</v>
       </c>
-      <c r="G156" s="10" t="n">
+      <c r="G162" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="H156" s="10" t="n">
+      <c r="H162" s="10" t="n">
         <v>82.85466505854929</v>
       </c>
-      <c r="I156" s="9" t="n">
+      <c r="I162" s="9" t="n">
         <v>507.097266231504</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="12" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B157" s="12" t="inlineStr">
+      <c r="B163" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C157" s="13" t="n">
+      <c r="C163" s="13" t="n">
         <v>1614.54275396197</v>
       </c>
-      <c r="D157" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="13" t="n">
+      <c r="D163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" s="13" t="n">
         <v>1614.54275396197</v>
       </c>
-      <c r="G157" s="12" t="inlineStr"/>
-      <c r="H157" s="12" t="inlineStr"/>
-      <c r="I157" s="12" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
+      <c r="G163" s="12" t="inlineStr"/>
+      <c r="H163" s="12" t="inlineStr"/>
+      <c r="I163" s="12" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C158" s="9" t="n">
+      <c r="C164" s="9" t="n">
         <v>19115.9660775389</v>
       </c>
-      <c r="D158" s="9" t="n">
+      <c r="D164" s="9" t="n">
         <v>19077.73414538382</v>
       </c>
-      <c r="E158" s="9" t="n">
+      <c r="E164" s="9" t="n">
         <v>18944.19000636614</v>
       </c>
-      <c r="F158" s="9" t="n">
+      <c r="F164" s="9" t="n">
         <v>38.23193215507854</v>
       </c>
-      <c r="G158" s="10" t="n">
+      <c r="G164" s="10" t="n">
         <v>99.8</v>
       </c>
-      <c r="H158" s="10" t="n">
+      <c r="H164" s="10" t="n">
         <v>99.3</v>
       </c>
-      <c r="I158" s="9" t="n">
+      <c r="I164" s="9" t="n">
         <v>197.6322301110262</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B159" s="12" t="inlineStr">
+      <c r="B165" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C159" s="13" t="n">
+      <c r="C165" s="13" t="n">
         <v>29764.24687693041</v>
       </c>
-      <c r="D159" s="13" t="n">
+      <c r="D165" s="13" t="n">
         <v>24406.68243908294</v>
       </c>
-      <c r="E159" s="13" t="n">
+      <c r="E165" s="13" t="n">
         <v>17084.67770735806</v>
       </c>
-      <c r="F159" s="13" t="n">
+      <c r="F165" s="13" t="n">
         <v>5357.564437847475</v>
       </c>
-      <c r="G159" s="14" t="n">
+      <c r="G165" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H159" s="14" t="n">
+      <c r="H165" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="I159" s="13" t="n">
+      <c r="I165" s="13" t="n">
         <v>334.8082234900225</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="15" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B160" s="15" t="inlineStr"/>
-      <c r="C160" s="16" t="n">
+      <c r="B166" s="15" t="inlineStr"/>
+      <c r="C166" s="16" t="n">
         <v>48880.21295446932</v>
       </c>
-      <c r="D160" s="16" t="n">
+      <c r="D166" s="16" t="n">
         <v>43484.41658446676</v>
       </c>
-      <c r="E160" s="16" t="n">
+      <c r="E166" s="16" t="n">
         <v>36028.86771372419</v>
       </c>
-      <c r="F160" s="16" t="n">
+      <c r="F166" s="16" t="n">
         <v>5395.796370002558</v>
       </c>
-      <c r="G160" s="15" t="inlineStr"/>
-      <c r="H160" s="15" t="inlineStr"/>
-      <c r="I160" s="15" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="15" t="inlineStr">
+      <c r="G166" s="15" t="inlineStr"/>
+      <c r="H166" s="15" t="inlineStr"/>
+      <c r="I166" s="15" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B161" s="15" t="inlineStr"/>
-      <c r="C161" s="16" t="n">
+      <c r="B167" s="15" t="inlineStr"/>
+      <c r="C167" s="16" t="n">
         <v>48880.21295446932</v>
       </c>
-      <c r="D161" s="16" t="n">
+      <c r="D167" s="16" t="n">
         <v>43484.41658446676</v>
       </c>
-      <c r="E161" s="16" t="n">
+      <c r="E167" s="16" t="n">
         <v>36028.86771372419</v>
       </c>
-      <c r="F161" s="16" t="n">
+      <c r="F167" s="16" t="n">
         <v>5395.796370002558</v>
       </c>
-      <c r="G161" s="15" t="inlineStr"/>
-      <c r="H161" s="15" t="inlineStr"/>
-      <c r="I161" s="15" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="15" t="inlineStr">
+      <c r="G167" s="15" t="inlineStr"/>
+      <c r="H167" s="15" t="inlineStr"/>
+      <c r="I167" s="15" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B162" s="15" t="inlineStr"/>
-      <c r="C162" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" s="15" t="inlineStr"/>
-      <c r="H162" s="15" t="inlineStr"/>
-      <c r="I162" s="15" t="inlineStr"/>
-    </row>
-    <row r="164" ht="17" customHeight="1">
-      <c r="A164" s="4" t="inlineStr">
+      <c r="B168" s="15" t="inlineStr"/>
+      <c r="C168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="15" t="inlineStr"/>
+      <c r="H168" s="15" t="inlineStr"/>
+      <c r="I168" s="15" t="inlineStr"/>
+    </row>
+    <row r="170" ht="17" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>A2 MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="5" t="n"/>
-      <c r="D164" s="5" t="n"/>
-      <c r="E164" s="5" t="n"/>
-      <c r="F164" s="5" t="n"/>
-      <c r="G164" s="5" t="n"/>
-      <c r="H164" s="5" t="n"/>
-      <c r="I164" s="5" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="6" t="inlineStr">
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+      <c r="E170" s="5" t="n"/>
+      <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="5" t="n"/>
+      <c r="I170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E171" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G165" s="6" t="inlineStr">
+      <c r="G171" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H165" s="6" t="inlineStr">
+      <c r="H171" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I165" s="6" t="inlineStr">
+      <c r="I171" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="8" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t>A2 Molasses (undiluted)</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C166" s="9" t="n">
+      <c r="C172" s="9" t="n">
         <v>29764.24687693041</v>
       </c>
-      <c r="D166" s="9" t="n">
+      <c r="D172" s="9" t="n">
         <v>24406.68243908294</v>
       </c>
-      <c r="E166" s="9" t="n">
+      <c r="E172" s="9" t="n">
         <v>17084.67770735806</v>
       </c>
-      <c r="F166" s="9" t="n">
+      <c r="F172" s="9" t="n">
         <v>5357.564437847475</v>
       </c>
-      <c r="G166" s="10" t="n">
+      <c r="G172" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="H166" s="10" t="n">
+      <c r="H172" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="I166" s="9" t="n">
+      <c r="I172" s="9" t="n">
         <v>334.8082234900225</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="12" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="12" t="inlineStr">
         <is>
           <t>Dilution Water</t>
         </is>
       </c>
-      <c r="B167" s="12" t="inlineStr">
+      <c r="B173" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C167" s="13" t="n">
+      <c r="C173" s="13" t="n">
         <v>5102.442321759496</v>
       </c>
-      <c r="D167" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F167" s="13" t="n">
+      <c r="D173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="13" t="n">
         <v>5102.442321759496</v>
       </c>
-      <c r="G167" s="12" t="inlineStr"/>
-      <c r="H167" s="12" t="inlineStr"/>
-      <c r="I167" s="12" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="8" t="inlineStr">
+      <c r="G173" s="12" t="inlineStr"/>
+      <c r="H173" s="12" t="inlineStr"/>
+      <c r="I173" s="12" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>A2 Molasses (diluted)</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C168" s="9" t="n">
+      <c r="C174" s="9" t="n">
         <v>34866.68919868991</v>
       </c>
-      <c r="D168" s="9" t="n">
+      <c r="D174" s="9" t="n">
         <v>24406.68243908294</v>
       </c>
-      <c r="E168" s="9" t="n">
+      <c r="E174" s="9" t="n">
         <v>17084.67770735805</v>
       </c>
-      <c r="F168" s="9" t="n">
+      <c r="F174" s="9" t="n">
         <v>10460.00675960697</v>
       </c>
-      <c r="G168" s="10" t="n">
+      <c r="G174" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H168" s="10" t="n">
+      <c r="H174" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="I168" s="9" t="n">
+      <c r="I174" s="9" t="n">
         <v>414.9005931382538</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="15" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B169" s="15" t="inlineStr"/>
-      <c r="C169" s="16" t="n">
+      <c r="B175" s="15" t="inlineStr"/>
+      <c r="C175" s="16" t="n">
         <v>34866.68919868991</v>
       </c>
-      <c r="D169" s="16" t="n">
+      <c r="D175" s="16" t="n">
         <v>24406.68243908294</v>
       </c>
-      <c r="E169" s="16" t="n">
+      <c r="E175" s="16" t="n">
         <v>17084.67770735806</v>
       </c>
-      <c r="F169" s="16" t="n">
+      <c r="F175" s="16" t="n">
         <v>10460.00675960697</v>
       </c>
-      <c r="G169" s="15" t="inlineStr"/>
-      <c r="H169" s="15" t="inlineStr"/>
-      <c r="I169" s="15" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="15" t="inlineStr">
+      <c r="G175" s="15" t="inlineStr"/>
+      <c r="H175" s="15" t="inlineStr"/>
+      <c r="I175" s="15" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B170" s="15" t="inlineStr"/>
-      <c r="C170" s="16" t="n">
+      <c r="B176" s="15" t="inlineStr"/>
+      <c r="C176" s="16" t="n">
         <v>34866.68919868991</v>
       </c>
-      <c r="D170" s="16" t="n">
+      <c r="D176" s="16" t="n">
         <v>24406.68243908294</v>
       </c>
-      <c r="E170" s="16" t="n">
+      <c r="E176" s="16" t="n">
         <v>17084.67770735805</v>
       </c>
-      <c r="F170" s="16" t="n">
+      <c r="F176" s="16" t="n">
         <v>10460.00675960697</v>
       </c>
-      <c r="G170" s="15" t="inlineStr"/>
-      <c r="H170" s="15" t="inlineStr"/>
-      <c r="I170" s="15" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="15" t="inlineStr">
+      <c r="G176" s="15" t="inlineStr"/>
+      <c r="H176" s="15" t="inlineStr"/>
+      <c r="I176" s="15" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B171" s="15" t="inlineStr"/>
-      <c r="C171" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" s="16" t="n">
+      <c r="B177" s="15" t="inlineStr"/>
+      <c r="C177" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" s="16" t="n">
         <v>3.637978807091713e-12</v>
       </c>
-      <c r="F171" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" s="15" t="inlineStr"/>
-      <c r="H171" s="15" t="inlineStr"/>
-      <c r="I171" s="15" t="inlineStr"/>
-    </row>
-    <row r="173" ht="17" customHeight="1">
-      <c r="A173" s="4" t="inlineStr">
+      <c r="F177" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="15" t="inlineStr"/>
+      <c r="H177" s="15" t="inlineStr"/>
+      <c r="I177" s="15" t="inlineStr"/>
+    </row>
+    <row r="179" ht="17" customHeight="1">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>B PANS  [B Pans]</t>
         </is>
       </c>
-      <c r="B173" s="5" t="n"/>
-      <c r="C173" s="5" t="n"/>
-      <c r="D173" s="5" t="n"/>
-      <c r="E173" s="5" t="n"/>
-      <c r="F173" s="5" t="n"/>
-      <c r="G173" s="5" t="n"/>
-      <c r="H173" s="5" t="n"/>
-      <c r="I173" s="5" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="6" t="inlineStr">
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="5" t="n"/>
+      <c r="I179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B174" s="6" t="inlineStr">
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C174" s="6" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D174" s="6" t="inlineStr">
+      <c r="D180" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E180" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G174" s="6" t="inlineStr">
+      <c r="G180" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="H180" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I174" s="6" t="inlineStr">
+      <c r="I180" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="8" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>A2 Molasses</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C175" s="9" t="n">
+      <c r="C181" s="9" t="n">
         <v>34866.68919868991</v>
       </c>
-      <c r="D175" s="9" t="n">
+      <c r="D181" s="9" t="n">
         <v>24406.68243908294</v>
       </c>
-      <c r="E175" s="9" t="n">
+      <c r="E181" s="9" t="n">
         <v>17084.67770735805</v>
       </c>
-      <c r="F175" s="9" t="n">
+      <c r="F181" s="9" t="n">
         <v>10460.00675960697</v>
       </c>
-      <c r="G175" s="10" t="n">
+      <c r="G181" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H175" s="10" t="n">
+      <c r="H181" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="I175" s="9" t="n">
+      <c r="I181" s="9" t="n">
         <v>414.9005931382538</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="12" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="12" t="inlineStr">
         <is>
           <t>C Magma</t>
         </is>
       </c>
-      <c r="B176" s="12" t="inlineStr">
+      <c r="B182" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C176" s="13" t="n">
+      <c r="C182" s="13" t="n">
         <v>10647.52040608454</v>
       </c>
-      <c r="D176" s="13" t="n">
+      <c r="D182" s="13" t="n">
         <v>9795.718773597779</v>
       </c>
-      <c r="E176" s="13" t="n">
+      <c r="E182" s="13" t="n">
         <v>8032.489394350178</v>
       </c>
-      <c r="F176" s="13" t="n">
+      <c r="F182" s="13" t="n">
         <v>851.801632486764</v>
       </c>
-      <c r="G176" s="14" t="n">
+      <c r="G182" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="H176" s="14" t="n">
+      <c r="H182" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="I176" s="13" t="n">
+      <c r="I182" s="13" t="n">
         <v>114.2336174895002</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="8" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>A1 Molasses</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C177" s="9" t="n">
+      <c r="C183" s="9" t="n">
         <v>6317.530268066492</v>
       </c>
-      <c r="D177" s="9" t="n">
+      <c r="D183" s="9" t="n">
         <v>4422.271187646545</v>
       </c>
-      <c r="E177" s="9" t="n">
+      <c r="E183" s="9" t="n">
         <v>3316.703390734908</v>
       </c>
-      <c r="F177" s="9" t="n">
+      <c r="F183" s="9" t="n">
         <v>1895.259080419947</v>
       </c>
-      <c r="G177" s="10" t="n">
+      <c r="G183" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="H177" s="10" t="n">
+      <c r="H183" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="I177" s="9" t="n">
+      <c r="I183" s="9" t="n">
         <v>75.17625319837212</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="12" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="12" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B178" s="12" t="inlineStr">
+      <c r="B184" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C178" s="13" t="n">
+      <c r="C184" s="13" t="n">
         <v>41090.07702162475</v>
       </c>
-      <c r="D178" s="13" t="n">
+      <c r="D184" s="13" t="n">
         <v>38624.67240032726</v>
       </c>
-      <c r="E178" s="13" t="n">
+      <c r="E184" s="13" t="n">
         <v>28433.87049244314</v>
       </c>
-      <c r="F178" s="13" t="n">
+      <c r="F184" s="13" t="n">
         <v>2465.404621297486</v>
       </c>
-      <c r="G178" s="14" t="n">
+      <c r="G184" s="14" t="n">
         <v>94</v>
       </c>
-      <c r="H178" s="14" t="n">
+      <c r="H184" s="14" t="n">
         <v>73.61582306184745</v>
       </c>
-      <c r="I178" s="13" t="n">
+      <c r="I184" s="13" t="n">
         <v>436.6767203738519</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C179" s="9" t="n">
+      <c r="C185" s="9" t="n">
         <v>10741.66285121619</v>
       </c>
-      <c r="D179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="9" t="n">
+      <c r="D185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="9" t="n">
         <v>10741.66285121619</v>
       </c>
-      <c r="G179" s="8" t="inlineStr"/>
-      <c r="H179" s="8" t="inlineStr"/>
-      <c r="I179" s="8" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="15" t="inlineStr">
+      <c r="G185" s="8" t="inlineStr"/>
+      <c r="H185" s="8" t="inlineStr"/>
+      <c r="I185" s="8" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B180" s="15" t="inlineStr"/>
-      <c r="C180" s="16" t="n">
+      <c r="B186" s="15" t="inlineStr"/>
+      <c r="C186" s="16" t="n">
         <v>51831.73987284094</v>
       </c>
-      <c r="D180" s="16" t="n">
+      <c r="D186" s="16" t="n">
         <v>38624.67240032726</v>
       </c>
-      <c r="E180" s="16" t="n">
+      <c r="E186" s="16" t="n">
         <v>28433.87049244314</v>
       </c>
-      <c r="F180" s="16" t="n">
+      <c r="F186" s="16" t="n">
         <v>13207.06747251368</v>
       </c>
-      <c r="G180" s="15" t="inlineStr"/>
-      <c r="H180" s="15" t="inlineStr"/>
-      <c r="I180" s="15" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="15" t="inlineStr">
+      <c r="G186" s="15" t="inlineStr"/>
+      <c r="H186" s="15" t="inlineStr"/>
+      <c r="I186" s="15" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B181" s="15" t="inlineStr"/>
-      <c r="C181" s="16" t="n">
+      <c r="B187" s="15" t="inlineStr"/>
+      <c r="C187" s="16" t="n">
         <v>51831.73987284094</v>
       </c>
-      <c r="D181" s="16" t="n">
+      <c r="D187" s="16" t="n">
         <v>38624.67240032726</v>
       </c>
-      <c r="E181" s="16" t="n">
+      <c r="E187" s="16" t="n">
         <v>28433.87049244314</v>
       </c>
-      <c r="F181" s="16" t="n">
+      <c r="F187" s="16" t="n">
         <v>13207.06747251368</v>
       </c>
-      <c r="G181" s="15" t="inlineStr"/>
-      <c r="H181" s="15" t="inlineStr"/>
-      <c r="I181" s="15" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="15" t="inlineStr">
+      <c r="G187" s="15" t="inlineStr"/>
+      <c r="H187" s="15" t="inlineStr"/>
+      <c r="I187" s="15" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B182" s="15" t="inlineStr"/>
-      <c r="C182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" s="15" t="inlineStr"/>
-      <c r="H182" s="15" t="inlineStr"/>
-      <c r="I182" s="15" t="inlineStr"/>
-    </row>
-    <row r="184" ht="17" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+      <c r="B188" s="15" t="inlineStr"/>
+      <c r="C188" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="15" t="inlineStr"/>
+      <c r="H188" s="15" t="inlineStr"/>
+      <c r="I188" s="15" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B189" s="20" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B190" s="21" t="n">
+        <v>29.696</v>
+      </c>
+      <c r="C190" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B191" s="22" t="n">
+        <v>12931.40514376126</v>
+      </c>
+      <c r="C191" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="17" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t>B CENTRIFUGALS  [B Centrifugals]</t>
         </is>
       </c>
-      <c r="B184" s="5" t="n"/>
-      <c r="C184" s="5" t="n"/>
-      <c r="D184" s="5" t="n"/>
-      <c r="E184" s="5" t="n"/>
-      <c r="F184" s="5" t="n"/>
-      <c r="G184" s="5" t="n"/>
-      <c r="H184" s="5" t="n"/>
-      <c r="I184" s="5" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="6" t="inlineStr">
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="5" t="n"/>
+      <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
+      <c r="H193" s="5" t="n"/>
+      <c r="I193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B185" s="6" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C185" s="6" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G185" s="6" t="inlineStr">
+      <c r="G194" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="H194" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I185" s="6" t="inlineStr">
+      <c r="I194" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="8" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C186" s="9" t="n">
+      <c r="C195" s="9" t="n">
         <v>41090.07702162475</v>
       </c>
-      <c r="D186" s="9" t="n">
+      <c r="D195" s="9" t="n">
         <v>38624.67240032726</v>
       </c>
-      <c r="E186" s="9" t="n">
+      <c r="E195" s="9" t="n">
         <v>28433.87049244314</v>
       </c>
-      <c r="F186" s="9" t="n">
+      <c r="F195" s="9" t="n">
         <v>2465.404621297486</v>
       </c>
-      <c r="G186" s="10" t="n">
+      <c r="G195" s="10" t="n">
         <v>94</v>
       </c>
-      <c r="H186" s="10" t="n">
+      <c r="H195" s="10" t="n">
         <v>73.61582306184745</v>
       </c>
-      <c r="I186" s="9" t="n">
+      <c r="I195" s="9" t="n">
         <v>436.6767203738519</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="12" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B187" s="12" t="inlineStr">
+      <c r="B196" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C187" s="13" t="n">
+      <c r="C196" s="13" t="n">
         <v>2529.949301767017</v>
       </c>
-      <c r="D187" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="13" t="n">
+      <c r="D196" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="13" t="n">
         <v>2529.949301767017</v>
       </c>
-      <c r="G187" s="12" t="inlineStr"/>
-      <c r="H187" s="12" t="inlineStr"/>
-      <c r="I187" s="12" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="8" t="inlineStr">
+      <c r="G196" s="12" t="inlineStr"/>
+      <c r="H196" s="12" t="inlineStr"/>
+      <c r="I196" s="12" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C188" s="9" t="n">
+      <c r="C197" s="9" t="n">
         <v>21971.16011650781</v>
       </c>
-      <c r="D188" s="9" t="n">
+      <c r="D197" s="9" t="n">
         <v>20872.60211068242</v>
       </c>
-      <c r="E188" s="9" t="n">
+      <c r="E197" s="9" t="n">
         <v>19202.79394182783</v>
       </c>
-      <c r="F188" s="9" t="n">
+      <c r="F197" s="9" t="n">
         <v>1098.558005825391</v>
       </c>
-      <c r="G188" s="10" t="n">
+      <c r="G197" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="H188" s="10" t="n">
+      <c r="H197" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="I188" s="9" t="n">
+      <c r="I197" s="9" t="n">
         <v>232.3882619616646</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="12" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B189" s="12" t="inlineStr">
+      <c r="B198" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C189" s="13" t="n">
+      <c r="C198" s="13" t="n">
         <v>21648.86620688395</v>
       </c>
-      <c r="D189" s="13" t="n">
+      <c r="D198" s="13" t="n">
         <v>17752.07028964484</v>
       </c>
-      <c r="E189" s="13" t="n">
+      <c r="E198" s="13" t="n">
         <v>9231.076550615318</v>
       </c>
-      <c r="F189" s="13" t="n">
+      <c r="F198" s="13" t="n">
         <v>3896.795917239113</v>
       </c>
-      <c r="G189" s="14" t="n">
+      <c r="G198" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H189" s="14" t="n">
+      <c r="H198" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="I189" s="13" t="n">
+      <c r="I198" s="13" t="n">
         <v>243.5209755271156</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="15" t="inlineStr">
-        <is>
-          <t>Total In</t>
-        </is>
-      </c>
-      <c r="B190" s="15" t="inlineStr"/>
-      <c r="C190" s="16" t="n">
-        <v>43620.02632339176</v>
-      </c>
-      <c r="D190" s="16" t="n">
-        <v>38624.67240032726</v>
-      </c>
-      <c r="E190" s="16" t="n">
-        <v>28433.87049244314</v>
-      </c>
-      <c r="F190" s="16" t="n">
-        <v>4995.353923064504</v>
-      </c>
-      <c r="G190" s="15" t="inlineStr"/>
-      <c r="H190" s="15" t="inlineStr"/>
-      <c r="I190" s="15" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="15" t="inlineStr">
-        <is>
-          <t>Total Out</t>
-        </is>
-      </c>
-      <c r="B191" s="15" t="inlineStr"/>
-      <c r="C191" s="16" t="n">
-        <v>43620.02632339176</v>
-      </c>
-      <c r="D191" s="16" t="n">
-        <v>38624.67240032726</v>
-      </c>
-      <c r="E191" s="16" t="n">
-        <v>28433.87049244314</v>
-      </c>
-      <c r="F191" s="16" t="n">
-        <v>4995.353923064504</v>
-      </c>
-      <c r="G191" s="15" t="inlineStr"/>
-      <c r="H191" s="15" t="inlineStr"/>
-      <c r="I191" s="15" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B192" s="15" t="inlineStr"/>
-      <c r="C192" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D192" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="15" t="inlineStr"/>
-      <c r="H192" s="15" t="inlineStr"/>
-      <c r="I192" s="15" t="inlineStr"/>
-    </row>
-    <row r="194" ht="17" customHeight="1">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>B MOLASSES DILUTION  (target 70.0 Bx)</t>
-        </is>
-      </c>
-      <c r="B194" s="5" t="n"/>
-      <c r="C194" s="5" t="n"/>
-      <c r="D194" s="5" t="n"/>
-      <c r="E194" s="5" t="n"/>
-      <c r="F194" s="5" t="n"/>
-      <c r="G194" s="5" t="n"/>
-      <c r="H194" s="5" t="n"/>
-      <c r="I194" s="5" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D195" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E195" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F195" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G195" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H195" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I195" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="8" t="inlineStr">
-        <is>
-          <t>B Molasses (undiluted)</t>
-        </is>
-      </c>
-      <c r="B196" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C196" s="9" t="n">
-        <v>21648.86620688395</v>
-      </c>
-      <c r="D196" s="9" t="n">
-        <v>17752.07028964484</v>
-      </c>
-      <c r="E196" s="9" t="n">
-        <v>9231.076550615318</v>
-      </c>
-      <c r="F196" s="9" t="n">
-        <v>3896.795917239113</v>
-      </c>
-      <c r="G196" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="H196" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="I196" s="9" t="n">
-        <v>243.5209755271156</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="12" t="inlineStr">
-        <is>
-          <t>Dilution Water</t>
-        </is>
-      </c>
-      <c r="B197" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C197" s="13" t="n">
-        <v>3711.234206894391</v>
-      </c>
-      <c r="D197" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E197" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" s="13" t="n">
-        <v>3711.234206894391</v>
-      </c>
-      <c r="G197" s="12" t="inlineStr"/>
-      <c r="H197" s="12" t="inlineStr"/>
-      <c r="I197" s="12" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t>B Molasses (diluted)</t>
-        </is>
-      </c>
-      <c r="B198" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C198" s="9" t="n">
-        <v>25360.10041377835</v>
-      </c>
-      <c r="D198" s="9" t="n">
-        <v>17752.07028964484</v>
-      </c>
-      <c r="E198" s="9" t="n">
-        <v>9231.076550615317</v>
-      </c>
-      <c r="F198" s="9" t="n">
-        <v>7608.030124133504</v>
-      </c>
-      <c r="G198" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="H198" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="I198" s="9" t="n">
-        <v>301.7757333873176</v>
       </c>
     </row>
     <row r="199">
@@ -4075,16 +3980,16 @@
       </c>
       <c r="B199" s="15" t="inlineStr"/>
       <c r="C199" s="16" t="n">
-        <v>25360.10041377835</v>
+        <v>43620.02632339176</v>
       </c>
       <c r="D199" s="16" t="n">
-        <v>17752.07028964484</v>
+        <v>38624.67240032726</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>9231.076550615318</v>
+        <v>28433.87049244314</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>7608.030124133504</v>
+        <v>4995.353923064504</v>
       </c>
       <c r="G199" s="15" t="inlineStr"/>
       <c r="H199" s="15" t="inlineStr"/>
@@ -4098,16 +4003,16 @@
       </c>
       <c r="B200" s="15" t="inlineStr"/>
       <c r="C200" s="16" t="n">
-        <v>25360.10041377835</v>
+        <v>43620.02632339176</v>
       </c>
       <c r="D200" s="16" t="n">
-        <v>17752.07028964484</v>
+        <v>38624.67240032726</v>
       </c>
       <c r="E200" s="16" t="n">
-        <v>9231.076550615317</v>
+        <v>28433.87049244314</v>
       </c>
       <c r="F200" s="16" t="n">
-        <v>7608.030124133504</v>
+        <v>4995.353923064504</v>
       </c>
       <c r="G200" s="15" t="inlineStr"/>
       <c r="H200" s="15" t="inlineStr"/>
@@ -4127,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="F201" s="16" t="n">
         <v>0</v>
@@ -4139,7 +4044,7 @@
     <row r="203" ht="17" customHeight="1">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>GRAIN PANS  [Grain Pans]</t>
+          <t>B MOLASSES DILUTION  (target 70.0 Bx)</t>
         </is>
       </c>
       <c r="B203" s="5" t="n"/>
@@ -4201,7 +4106,7 @@
     <row r="205">
       <c r="A205" s="8" t="inlineStr">
         <is>
-          <t>Syrup</t>
+          <t>B Molasses (undiluted)</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
@@ -4210,31 +4115,31 @@
         </is>
       </c>
       <c r="C205" s="9" t="n">
-        <v>5509.49608494404</v>
+        <v>21648.86620688395</v>
       </c>
       <c r="D205" s="9" t="n">
-        <v>3581.172455213627</v>
+        <v>17752.07028964484</v>
       </c>
       <c r="E205" s="9" t="n">
-        <v>3184.934010329539</v>
+        <v>9231.076550615318</v>
       </c>
       <c r="F205" s="9" t="n">
-        <v>1928.323629730414</v>
+        <v>3896.795917239113</v>
       </c>
       <c r="G205" s="10" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="H205" s="10" t="n">
-        <v>88.93551065078627</v>
+        <v>52</v>
       </c>
       <c r="I205" s="9" t="n">
-        <v>67.09816496264268</v>
+        <v>243.5209755271156</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="12" t="inlineStr">
         <is>
-          <t>A1 Molasses</t>
+          <t>Dilution Water</t>
         </is>
       </c>
       <c r="B206" s="12" t="inlineStr">
@@ -4243,428 +4148,418 @@
         </is>
       </c>
       <c r="C206" s="13" t="n">
-        <v>1114.858282599969</v>
+        <v>3711.234206894391</v>
       </c>
       <c r="D206" s="13" t="n">
-        <v>780.4007978199784</v>
+        <v>0</v>
       </c>
       <c r="E206" s="13" t="n">
-        <v>585.3005983649838</v>
+        <v>0</v>
       </c>
       <c r="F206" s="13" t="n">
-        <v>334.4574847799906</v>
-      </c>
-      <c r="G206" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="H206" s="14" t="n">
-        <v>75</v>
-      </c>
-      <c r="I206" s="13" t="n">
-        <v>13.26639762324214</v>
-      </c>
+        <v>3711.234206894391</v>
+      </c>
+      <c r="G206" s="12" t="inlineStr"/>
+      <c r="H206" s="12" t="inlineStr"/>
+      <c r="I206" s="12" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="8" t="inlineStr">
         <is>
-          <t>A2 Molasses</t>
+          <t>B Molasses (diluted)</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>In</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="C207" s="9" t="n">
-        <v>0</v>
+        <v>25360.10041377835</v>
       </c>
       <c r="D207" s="9" t="n">
-        <v>0</v>
+        <v>17752.07028964484</v>
       </c>
       <c r="E207" s="9" t="n">
-        <v>0</v>
+        <v>9231.076550615317</v>
       </c>
       <c r="F207" s="9" t="n">
-        <v>0</v>
+        <v>7608.030124133504</v>
       </c>
       <c r="G207" s="10" t="n">
         <v>70</v>
       </c>
       <c r="H207" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="I207" s="9" t="n">
+        <v>301.7757333873176</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B208" s="15" t="inlineStr"/>
+      <c r="C208" s="16" t="n">
+        <v>25360.10041377835</v>
+      </c>
+      <c r="D208" s="16" t="n">
+        <v>17752.07028964484</v>
+      </c>
+      <c r="E208" s="16" t="n">
+        <v>9231.076550615318</v>
+      </c>
+      <c r="F208" s="16" t="n">
+        <v>7608.030124133504</v>
+      </c>
+      <c r="G208" s="15" t="inlineStr"/>
+      <c r="H208" s="15" t="inlineStr"/>
+      <c r="I208" s="15" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B209" s="15" t="inlineStr"/>
+      <c r="C209" s="16" t="n">
+        <v>25360.10041377835</v>
+      </c>
+      <c r="D209" s="16" t="n">
+        <v>17752.07028964484</v>
+      </c>
+      <c r="E209" s="16" t="n">
+        <v>9231.076550615317</v>
+      </c>
+      <c r="F209" s="16" t="n">
+        <v>7608.030124133504</v>
+      </c>
+      <c r="G209" s="15" t="inlineStr"/>
+      <c r="H209" s="15" t="inlineStr"/>
+      <c r="I209" s="15" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>Net (In - Out)</t>
+        </is>
+      </c>
+      <c r="B210" s="15" t="inlineStr"/>
+      <c r="C210" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" s="16" t="n">
+        <v>1.818989403545856e-12</v>
+      </c>
+      <c r="F210" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="15" t="inlineStr"/>
+      <c r="H210" s="15" t="inlineStr"/>
+      <c r="I210" s="15" t="inlineStr"/>
+    </row>
+    <row r="212" ht="17" customHeight="1">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>GRAIN PANS  [Grain Pans]</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>Syrup</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="n">
+        <v>5509.49608494404</v>
+      </c>
+      <c r="D214" s="9" t="n">
+        <v>3581.172455213627</v>
+      </c>
+      <c r="E214" s="9" t="n">
+        <v>3184.934010329539</v>
+      </c>
+      <c r="F214" s="9" t="n">
+        <v>1928.323629730414</v>
+      </c>
+      <c r="G214" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="H214" s="10" t="n">
+        <v>88.93551065078627</v>
+      </c>
+      <c r="I214" s="9" t="n">
+        <v>67.09816496264268</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="12" t="inlineStr">
+        <is>
+          <t>A1 Molasses</t>
+        </is>
+      </c>
+      <c r="B215" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C215" s="13" t="n">
+        <v>1114.858282599969</v>
+      </c>
+      <c r="D215" s="13" t="n">
+        <v>780.4007978199784</v>
+      </c>
+      <c r="E215" s="13" t="n">
+        <v>585.3005983649838</v>
+      </c>
+      <c r="F215" s="13" t="n">
+        <v>334.4574847799906</v>
+      </c>
+      <c r="G215" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="I207" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="12" t="inlineStr">
+      <c r="H215" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="I215" s="13" t="n">
+        <v>13.26639762324214</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>A2 Molasses</t>
+        </is>
+      </c>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H216" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="I216" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="12" t="inlineStr">
         <is>
           <t>B Molasses</t>
         </is>
       </c>
-      <c r="B208" s="12" t="inlineStr">
+      <c r="B217" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C208" s="13" t="n">
+      <c r="C217" s="13" t="n">
         <v>2536.010041377835</v>
       </c>
-      <c r="D208" s="13" t="n">
+      <c r="D217" s="13" t="n">
         <v>1775.207028964484</v>
       </c>
-      <c r="E208" s="13" t="n">
+      <c r="E217" s="13" t="n">
         <v>923.1076550615317</v>
       </c>
-      <c r="F208" s="13" t="n">
+      <c r="F217" s="13" t="n">
         <v>760.8030124133502</v>
       </c>
-      <c r="G208" s="14" t="n">
+      <c r="G217" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="H208" s="14" t="n">
+      <c r="H217" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="I208" s="13" t="n">
+      <c r="I217" s="13" t="n">
         <v>30.17757333873176</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="8" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
         <is>
           <t>Massecuite Out</t>
         </is>
       </c>
-      <c r="B209" s="8" t="inlineStr">
+      <c r="B218" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C209" s="9" t="n">
+      <c r="C218" s="9" t="n">
         <v>6973.613956816012</v>
       </c>
-      <c r="D209" s="9" t="n">
+      <c r="D218" s="9" t="n">
         <v>6136.78028199809</v>
       </c>
-      <c r="E209" s="9" t="n">
+      <c r="E218" s="9" t="n">
         <v>4693.342263756054</v>
       </c>
-      <c r="F209" s="9" t="n">
+      <c r="F218" s="9" t="n">
         <v>836.8336748179217</v>
       </c>
-      <c r="G209" s="10" t="n">
+      <c r="G218" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="H209" s="10" t="n">
+      <c r="H218" s="10" t="n">
         <v>76.47890340026868</v>
       </c>
-      <c r="I209" s="9" t="n">
+      <c r="I218" s="9" t="n">
         <v>76.24992806042802</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="12" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="12" t="inlineStr">
         <is>
           <t>Evaporated Water</t>
         </is>
       </c>
-      <c r="B210" s="12" t="inlineStr">
+      <c r="B219" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C210" s="13" t="n">
+      <c r="C219" s="13" t="n">
         <v>2186.750452105832</v>
       </c>
-      <c r="D210" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E210" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F210" s="13" t="n">
+      <c r="D219" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="13" t="n">
         <v>2186.750452105832</v>
       </c>
-      <c r="G210" s="12" t="inlineStr"/>
-      <c r="H210" s="12" t="inlineStr"/>
-      <c r="I210" s="12" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="15" t="inlineStr">
+      <c r="G219" s="12" t="inlineStr"/>
+      <c r="H219" s="12" t="inlineStr"/>
+      <c r="I219" s="12" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B211" s="15" t="inlineStr"/>
-      <c r="C211" s="16" t="n">
+      <c r="B220" s="15" t="inlineStr"/>
+      <c r="C220" s="16" t="n">
         <v>9160.364408921843</v>
       </c>
-      <c r="D211" s="16" t="n">
+      <c r="D220" s="16" t="n">
         <v>6136.78028199809</v>
       </c>
-      <c r="E211" s="16" t="n">
+      <c r="E220" s="16" t="n">
         <v>4693.342263756054</v>
       </c>
-      <c r="F211" s="16" t="n">
+      <c r="F220" s="16" t="n">
         <v>3023.584126923754</v>
       </c>
-      <c r="G211" s="15" t="inlineStr"/>
-      <c r="H211" s="15" t="inlineStr"/>
-      <c r="I211" s="15" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="15" t="inlineStr">
-        <is>
-          <t>Total Out</t>
-        </is>
-      </c>
-      <c r="B212" s="15" t="inlineStr"/>
-      <c r="C212" s="16" t="n">
-        <v>9160.364408921843</v>
-      </c>
-      <c r="D212" s="16" t="n">
-        <v>6136.78028199809</v>
-      </c>
-      <c r="E212" s="16" t="n">
-        <v>4693.342263756054</v>
-      </c>
-      <c r="F212" s="16" t="n">
-        <v>3023.584126923754</v>
-      </c>
-      <c r="G212" s="15" t="inlineStr"/>
-      <c r="H212" s="15" t="inlineStr"/>
-      <c r="I212" s="15" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="15" t="inlineStr">
-        <is>
-          <t>Net (In - Out)</t>
-        </is>
-      </c>
-      <c r="B213" s="15" t="inlineStr"/>
-      <c r="C213" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D213" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F213" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" s="15" t="inlineStr"/>
-      <c r="H213" s="15" t="inlineStr"/>
-      <c r="I213" s="15" t="inlineStr"/>
-    </row>
-    <row r="215" ht="17" customHeight="1">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>C PANS  [C Pans]</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="n"/>
-      <c r="C215" s="5" t="n"/>
-      <c r="D215" s="5" t="n"/>
-      <c r="E215" s="5" t="n"/>
-      <c r="F215" s="5" t="n"/>
-      <c r="G215" s="5" t="n"/>
-      <c r="H215" s="5" t="n"/>
-      <c r="I215" s="5" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D216" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E216" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G216" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H216" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I216" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="8" t="inlineStr">
-        <is>
-          <t>Grain Massecuite</t>
-        </is>
-      </c>
-      <c r="B217" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C217" s="9" t="n">
-        <v>6973.613956816012</v>
-      </c>
-      <c r="D217" s="9" t="n">
-        <v>6136.78028199809</v>
-      </c>
-      <c r="E217" s="9" t="n">
-        <v>4693.342263756055</v>
-      </c>
-      <c r="F217" s="9" t="n">
-        <v>836.8336748179217</v>
-      </c>
-      <c r="G217" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="H217" s="10" t="n">
-        <v>76.47890340026868</v>
-      </c>
-      <c r="I217" s="9" t="n">
-        <v>76.24992806042802</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="12" t="inlineStr">
-        <is>
-          <t>B Molasses</t>
-        </is>
-      </c>
-      <c r="B218" s="12" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C218" s="13" t="n">
-        <v>22824.09037240051</v>
-      </c>
-      <c r="D218" s="13" t="n">
-        <v>15976.86326068036</v>
-      </c>
-      <c r="E218" s="13" t="n">
-        <v>8307.968895553786</v>
-      </c>
-      <c r="F218" s="13" t="n">
-        <v>6847.227111720153</v>
-      </c>
-      <c r="G218" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="H218" s="14" t="n">
-        <v>52</v>
-      </c>
-      <c r="I218" s="13" t="n">
-        <v>271.5981600485858</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite Out</t>
-        </is>
-      </c>
-      <c r="B219" s="8" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C219" s="9" t="n">
-        <v>23155.64768866853</v>
-      </c>
-      <c r="D219" s="9" t="n">
-        <v>22113.64354267845</v>
-      </c>
-      <c r="E219" s="9" t="n">
-        <v>13001.31115930984</v>
-      </c>
-      <c r="F219" s="9" t="n">
-        <v>1042.004145990086</v>
-      </c>
-      <c r="G219" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H219" s="10" t="n">
-        <v>58.79316601182356</v>
-      </c>
-      <c r="I219" s="9" t="n">
-        <v>244.3357752720343</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="12" t="inlineStr">
-        <is>
-          <t>Evaporated Water</t>
-        </is>
-      </c>
-      <c r="B220" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C220" s="13" t="n">
-        <v>6642.056640547988</v>
-      </c>
-      <c r="D220" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E220" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F220" s="13" t="n">
-        <v>6642.056640547988</v>
-      </c>
-      <c r="G220" s="12" t="inlineStr"/>
-      <c r="H220" s="12" t="inlineStr"/>
-      <c r="I220" s="12" t="inlineStr"/>
+      <c r="G220" s="15" t="inlineStr"/>
+      <c r="H220" s="15" t="inlineStr"/>
+      <c r="I220" s="15" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="15" t="inlineStr">
         <is>
-          <t>Total In</t>
+          <t>Total Out</t>
         </is>
       </c>
       <c r="B221" s="15" t="inlineStr"/>
       <c r="C221" s="16" t="n">
-        <v>29797.70432921652</v>
+        <v>9160.364408921843</v>
       </c>
       <c r="D221" s="16" t="n">
-        <v>22113.64354267845</v>
+        <v>6136.78028199809</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>13001.31115930984</v>
+        <v>4693.342263756054</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>7684.060786538073</v>
+        <v>3023.584126923754</v>
       </c>
       <c r="G221" s="15" t="inlineStr"/>
       <c r="H221" s="15" t="inlineStr"/>
@@ -4673,978 +4568,1296 @@
     <row r="222">
       <c r="A222" s="15" t="inlineStr">
         <is>
-          <t>Total Out</t>
+          <t>Net (In - Out)</t>
         </is>
       </c>
       <c r="B222" s="15" t="inlineStr"/>
       <c r="C222" s="16" t="n">
-        <v>29797.70432921652</v>
+        <v>0</v>
       </c>
       <c r="D222" s="16" t="n">
-        <v>22113.64354267845</v>
+        <v>0</v>
       </c>
       <c r="E222" s="16" t="n">
-        <v>13001.31115930984</v>
+        <v>0</v>
       </c>
       <c r="F222" s="16" t="n">
-        <v>7684.060786538073</v>
+        <v>0</v>
       </c>
       <c r="G222" s="15" t="inlineStr"/>
       <c r="H222" s="15" t="inlineStr"/>
       <c r="I222" s="15" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="15" t="inlineStr">
+      <c r="A223" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B223" s="20" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B224" s="21" t="n">
+        <v>29.696</v>
+      </c>
+      <c r="C224" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B225" s="22" t="n">
+        <v>2639.345673680247</v>
+      </c>
+      <c r="C225" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="17" customHeight="1">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>C PANS  [C Pans]</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
+      <c r="F227" s="5" t="n"/>
+      <c r="G227" s="5" t="n"/>
+      <c r="H227" s="5" t="n"/>
+      <c r="I227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>Grain Massecuite</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="n">
+        <v>6973.613956816012</v>
+      </c>
+      <c r="D229" s="9" t="n">
+        <v>6136.78028199809</v>
+      </c>
+      <c r="E229" s="9" t="n">
+        <v>4693.342263756055</v>
+      </c>
+      <c r="F229" s="9" t="n">
+        <v>836.8336748179217</v>
+      </c>
+      <c r="G229" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="H229" s="10" t="n">
+        <v>76.47890340026868</v>
+      </c>
+      <c r="I229" s="9" t="n">
+        <v>76.24992806042802</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>B Molasses</t>
+        </is>
+      </c>
+      <c r="B230" s="12" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C230" s="13" t="n">
+        <v>22824.09037240051</v>
+      </c>
+      <c r="D230" s="13" t="n">
+        <v>15976.86326068036</v>
+      </c>
+      <c r="E230" s="13" t="n">
+        <v>8307.968895553786</v>
+      </c>
+      <c r="F230" s="13" t="n">
+        <v>6847.227111720153</v>
+      </c>
+      <c r="G230" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="H230" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="I230" s="13" t="n">
+        <v>271.5981600485858</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite Out</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="n">
+        <v>23155.64768866853</v>
+      </c>
+      <c r="D231" s="9" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E231" s="9" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F231" s="9" t="n">
+        <v>1042.004145990086</v>
+      </c>
+      <c r="G231" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H231" s="10" t="n">
+        <v>58.79316601182356</v>
+      </c>
+      <c r="I231" s="9" t="n">
+        <v>244.3357752720343</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="12" t="inlineStr">
+        <is>
+          <t>Evaporated Water</t>
+        </is>
+      </c>
+      <c r="B232" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C232" s="13" t="n">
+        <v>6642.056640547988</v>
+      </c>
+      <c r="D232" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" s="13" t="n">
+        <v>6642.056640547988</v>
+      </c>
+      <c r="G232" s="12" t="inlineStr"/>
+      <c r="H232" s="12" t="inlineStr"/>
+      <c r="I232" s="12" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>Total In</t>
+        </is>
+      </c>
+      <c r="B233" s="15" t="inlineStr"/>
+      <c r="C233" s="16" t="n">
+        <v>29797.70432921652</v>
+      </c>
+      <c r="D233" s="16" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E233" s="16" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F233" s="16" t="n">
+        <v>7684.060786538073</v>
+      </c>
+      <c r="G233" s="15" t="inlineStr"/>
+      <c r="H233" s="15" t="inlineStr"/>
+      <c r="I233" s="15" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>Total Out</t>
+        </is>
+      </c>
+      <c r="B234" s="15" t="inlineStr"/>
+      <c r="C234" s="16" t="n">
+        <v>29797.70432921652</v>
+      </c>
+      <c r="D234" s="16" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E234" s="16" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F234" s="16" t="n">
+        <v>7684.060786538073</v>
+      </c>
+      <c r="G234" s="15" t="inlineStr"/>
+      <c r="H234" s="15" t="inlineStr"/>
+      <c r="I234" s="15" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B223" s="15" t="inlineStr"/>
-      <c r="C223" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D223" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E223" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F223" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" s="15" t="inlineStr"/>
-      <c r="H223" s="15" t="inlineStr"/>
-      <c r="I223" s="15" t="inlineStr"/>
-    </row>
-    <row r="225" ht="17" customHeight="1">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>C CRYSTALLIZERS  [C Crystallizers]</t>
-        </is>
-      </c>
-      <c r="B225" s="5" t="n"/>
-      <c r="C225" s="5" t="n"/>
-      <c r="D225" s="5" t="n"/>
-      <c r="E225" s="5" t="n"/>
-      <c r="F225" s="5" t="n"/>
-      <c r="G225" s="5" t="n"/>
-      <c r="H225" s="5" t="n"/>
-      <c r="I225" s="5" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C226" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H226" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I226" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite In  (T=173.0 °F)</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C227" s="9" t="n">
-        <v>23155.64768866853</v>
-      </c>
-      <c r="D227" s="9" t="n">
-        <v>22113.64354267845</v>
-      </c>
-      <c r="E227" s="9" t="n">
-        <v>13001.31115930984</v>
-      </c>
-      <c r="F227" s="9" t="n">
-        <v>1042.004145990086</v>
-      </c>
-      <c r="G227" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H227" s="10" t="n">
-        <v>58.79316601182356</v>
-      </c>
-      <c r="I227" s="9" t="n">
-        <v>244.3357752720343</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="12" t="inlineStr">
-        <is>
-          <t>Massecuite Out  (T=120.0 °F)</t>
-        </is>
-      </c>
-      <c r="B228" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C228" s="13" t="n">
-        <v>23155.64768866853</v>
-      </c>
-      <c r="D228" s="13" t="n">
-        <v>22113.64354267845</v>
-      </c>
-      <c r="E228" s="13" t="n">
-        <v>13001.31115930984</v>
-      </c>
-      <c r="F228" s="13" t="n">
-        <v>1042.004145990086</v>
-      </c>
-      <c r="G228" s="14" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H228" s="14" t="n">
-        <v>58.79316601182356</v>
-      </c>
-      <c r="I228" s="13" t="n">
-        <v>244.3357752720343</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="17" t="inlineStr">
-        <is>
-          <t>ML purity in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B229" s="20" t="inlineStr">
-        <is>
-          <t>33.0 -&gt; 30.0</t>
-        </is>
-      </c>
-      <c r="C229" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="17" t="inlineStr">
-        <is>
-          <t>Crystal content in -&gt; out</t>
-        </is>
-      </c>
-      <c r="B230" s="20" t="inlineStr">
-        <is>
-          <t>36.8 -&gt; 39.3</t>
-        </is>
-      </c>
-      <c r="C230" s="19" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="17" t="inlineStr">
-        <is>
-          <t>Duty</t>
-        </is>
-      </c>
-      <c r="B231" s="21" t="n">
-        <v>559688.278632685</v>
-      </c>
-      <c r="C231" s="19" t="inlineStr">
-        <is>
-          <t>BTU/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="17" t="inlineStr">
-        <is>
-          <t>Cooling Water</t>
-        </is>
-      </c>
-      <c r="B232" s="21" t="n">
-        <v>27984.41393163425</v>
-      </c>
-      <c r="C232" s="19" t="inlineStr">
-        <is>
-          <t>lb/hr  (56 gpm, 85 -&gt; 105 °F)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="17" customHeight="1">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>C REHEATERS  [C Reheaters]</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="n"/>
-      <c r="C234" s="5" t="n"/>
-      <c r="D234" s="5" t="n"/>
-      <c r="E234" s="5" t="n"/>
-      <c r="F234" s="5" t="n"/>
-      <c r="G234" s="5" t="n"/>
-      <c r="H234" s="5" t="n"/>
-      <c r="I234" s="5" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>Stream</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>Dir</t>
-        </is>
-      </c>
-      <c r="C235" s="6" t="inlineStr">
-        <is>
-          <t>Flow (lb/hr)</t>
-        </is>
-      </c>
-      <c r="D235" s="6" t="inlineStr">
-        <is>
-          <t>Solids (lb/hr)</t>
-        </is>
-      </c>
-      <c r="E235" s="6" t="inlineStr">
-        <is>
-          <t>Pol (lb/hr)</t>
-        </is>
-      </c>
-      <c r="F235" s="6" t="inlineStr">
-        <is>
-          <t>Water (lb/hr)</t>
-        </is>
-      </c>
-      <c r="G235" s="6" t="inlineStr">
-        <is>
-          <t>Brix %</t>
-        </is>
-      </c>
-      <c r="H235" s="6" t="inlineStr">
-        <is>
-          <t>Purity %</t>
-        </is>
-      </c>
-      <c r="I235" s="6" t="inlineStr">
-        <is>
-          <t>ft³/hr</t>
-        </is>
-      </c>
+      <c r="B235" s="15" t="inlineStr"/>
+      <c r="C235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="15" t="inlineStr"/>
+      <c r="H235" s="15" t="inlineStr"/>
+      <c r="I235" s="15" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="8" t="inlineStr">
-        <is>
-          <t>Massecuite In  (T=120.0 °F)</t>
-        </is>
-      </c>
-      <c r="B236" s="8" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="C236" s="9" t="n">
-        <v>23155.64768866853</v>
-      </c>
-      <c r="D236" s="9" t="n">
-        <v>22113.64354267845</v>
-      </c>
-      <c r="E236" s="9" t="n">
-        <v>13001.31115930984</v>
-      </c>
-      <c r="F236" s="9" t="n">
-        <v>1042.004145990086</v>
-      </c>
-      <c r="G236" s="10" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H236" s="10" t="n">
-        <v>58.79316601182356</v>
-      </c>
-      <c r="I236" s="9" t="n">
-        <v>244.3357752720343</v>
+      <c r="A236" s="17" t="inlineStr">
+        <is>
+          <t>Calandria steam type</t>
+        </is>
+      </c>
+      <c r="B236" s="20" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="12" t="inlineStr">
-        <is>
-          <t>Massecuite Out  (T=130.0 °F)</t>
-        </is>
-      </c>
-      <c r="B237" s="12" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="C237" s="13" t="n">
-        <v>23155.64768866853</v>
-      </c>
-      <c r="D237" s="13" t="n">
-        <v>22113.64354267845</v>
-      </c>
-      <c r="E237" s="13" t="n">
-        <v>13001.31115930984</v>
-      </c>
-      <c r="F237" s="13" t="n">
-        <v>1042.004145990086</v>
-      </c>
-      <c r="G237" s="14" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="H237" s="14" t="n">
-        <v>58.79316601182356</v>
-      </c>
-      <c r="I237" s="13" t="n">
-        <v>244.3357752720343</v>
+      <c r="A237" s="17" t="inlineStr">
+        <is>
+          <t>Calandria pressure</t>
+        </is>
+      </c>
+      <c r="B237" s="21" t="n">
+        <v>21.696</v>
+      </c>
+      <c r="C237" s="19" t="inlineStr">
+        <is>
+          <t>psia</t>
+        </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="17" t="inlineStr">
         <is>
+          <t>Calandria steam flow</t>
+        </is>
+      </c>
+      <c r="B238" s="22" t="n">
+        <v>7757.766823725374</v>
+      </c>
+      <c r="C238" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="17" customHeight="1">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>C CRYSTALLIZERS  [C Crystallizers]</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
+      <c r="F240" s="5" t="n"/>
+      <c r="G240" s="5" t="n"/>
+      <c r="H240" s="5" t="n"/>
+      <c r="I240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H241" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I241" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite In  (T=173.0 °F)</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="n">
+        <v>23155.64768866853</v>
+      </c>
+      <c r="D242" s="9" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E242" s="9" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F242" s="9" t="n">
+        <v>1042.004145990086</v>
+      </c>
+      <c r="G242" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H242" s="10" t="n">
+        <v>58.79316601182356</v>
+      </c>
+      <c r="I242" s="9" t="n">
+        <v>244.3357752720343</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out  (T=120.0 °F)</t>
+        </is>
+      </c>
+      <c r="B243" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C243" s="13" t="n">
+        <v>23155.64768866853</v>
+      </c>
+      <c r="D243" s="13" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E243" s="13" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F243" s="13" t="n">
+        <v>1042.004145990086</v>
+      </c>
+      <c r="G243" s="14" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H243" s="14" t="n">
+        <v>58.79316601182356</v>
+      </c>
+      <c r="I243" s="13" t="n">
+        <v>244.3357752720343</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="17" t="inlineStr">
+        <is>
           <t>ML purity in -&gt; out</t>
         </is>
       </c>
-      <c r="B238" s="20" t="inlineStr">
+      <c r="B244" s="20" t="inlineStr">
+        <is>
+          <t>33.0 -&gt; 30.0</t>
+        </is>
+      </c>
+      <c r="C244" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="17" t="inlineStr">
+        <is>
+          <t>Crystal content in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B245" s="20" t="inlineStr">
+        <is>
+          <t>36.8 -&gt; 39.3</t>
+        </is>
+      </c>
+      <c r="C245" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="17" t="inlineStr">
+        <is>
+          <t>Duty</t>
+        </is>
+      </c>
+      <c r="B246" s="22" t="n">
+        <v>559688.278632685</v>
+      </c>
+      <c r="C246" s="19" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t>Cooling Water</t>
+        </is>
+      </c>
+      <c r="B247" s="22" t="n">
+        <v>27984.41393163425</v>
+      </c>
+      <c r="C247" s="19" t="inlineStr">
+        <is>
+          <t>lb/hr  (56 gpm, 85 -&gt; 105 °F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="17" customHeight="1">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>C REHEATERS  [C Reheaters]</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="5" t="n"/>
+      <c r="F249" s="5" t="n"/>
+      <c r="G249" s="5" t="n"/>
+      <c r="H249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>Stream</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>Flow (lb/hr)</t>
+        </is>
+      </c>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>Solids (lb/hr)</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>Pol (lb/hr)</t>
+        </is>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>Water (lb/hr)</t>
+        </is>
+      </c>
+      <c r="G250" s="6" t="inlineStr">
+        <is>
+          <t>Brix %</t>
+        </is>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="I250" s="6" t="inlineStr">
+        <is>
+          <t>ft³/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>Massecuite In  (T=120.0 °F)</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="C251" s="9" t="n">
+        <v>23155.64768866853</v>
+      </c>
+      <c r="D251" s="9" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E251" s="9" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F251" s="9" t="n">
+        <v>1042.004145990086</v>
+      </c>
+      <c r="G251" s="10" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H251" s="10" t="n">
+        <v>58.79316601182356</v>
+      </c>
+      <c r="I251" s="9" t="n">
+        <v>244.3357752720343</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="12" t="inlineStr">
+        <is>
+          <t>Massecuite Out  (T=130.0 °F)</t>
+        </is>
+      </c>
+      <c r="B252" s="12" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="C252" s="13" t="n">
+        <v>23155.64768866853</v>
+      </c>
+      <c r="D252" s="13" t="n">
+        <v>22113.64354267845</v>
+      </c>
+      <c r="E252" s="13" t="n">
+        <v>13001.31115930984</v>
+      </c>
+      <c r="F252" s="13" t="n">
+        <v>1042.004145990086</v>
+      </c>
+      <c r="G252" s="14" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H252" s="14" t="n">
+        <v>58.79316601182356</v>
+      </c>
+      <c r="I252" s="13" t="n">
+        <v>244.3357752720343</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="17" t="inlineStr">
+        <is>
+          <t>ML purity in -&gt; out</t>
+        </is>
+      </c>
+      <c r="B253" s="20" t="inlineStr">
         <is>
           <t>30.0 -&gt; 30.0</t>
         </is>
       </c>
-      <c r="C238" s="19" t="inlineStr">
+      <c r="C253" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="17" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="17" t="inlineStr">
         <is>
           <t>Crystal content in -&gt; out</t>
         </is>
       </c>
-      <c r="B239" s="20" t="inlineStr">
+      <c r="B254" s="20" t="inlineStr">
         <is>
           <t>39.3 -&gt; 39.3</t>
         </is>
       </c>
-      <c r="C239" s="19" t="inlineStr">
+      <c r="C254" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="17" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="17" t="inlineStr">
         <is>
           <t>Duty</t>
         </is>
       </c>
-      <c r="B240" s="21" t="n">
+      <c r="B255" s="22" t="n">
         <v>105648.105692504</v>
       </c>
-      <c r="C240" s="19" t="inlineStr">
+      <c r="C255" s="19" t="inlineStr">
         <is>
           <t>BTU/hr</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="17" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="17" t="inlineStr">
         <is>
           <t>Hot Water</t>
         </is>
       </c>
-      <c r="B241" s="21" t="n">
+      <c r="B256" s="22" t="n">
         <v>7043.207046166931</v>
       </c>
-      <c r="C241" s="19" t="inlineStr">
+      <c r="C256" s="19" t="inlineStr">
         <is>
           <t>lb/hr  (14 gpm, 150 -&gt; 135 °F)</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="17" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
+    <row r="258" ht="17" customHeight="1">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>C CENTRIFUGALS  [C Centrifugals]</t>
         </is>
       </c>
-      <c r="B243" s="5" t="n"/>
-      <c r="C243" s="5" t="n"/>
-      <c r="D243" s="5" t="n"/>
-      <c r="E243" s="5" t="n"/>
-      <c r="F243" s="5" t="n"/>
-      <c r="G243" s="5" t="n"/>
-      <c r="H243" s="5" t="n"/>
-      <c r="I243" s="5" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="6" t="inlineStr">
+      <c r="B258" s="5" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="5" t="n"/>
+      <c r="F258" s="5" t="n"/>
+      <c r="G258" s="5" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="B259" s="6" t="inlineStr">
         <is>
           <t>Dir</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
+      <c r="C259" s="6" t="inlineStr">
         <is>
           <t>Flow (lb/hr)</t>
         </is>
       </c>
-      <c r="D244" s="6" t="inlineStr">
+      <c r="D259" s="6" t="inlineStr">
         <is>
           <t>Solids (lb/hr)</t>
         </is>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E259" s="6" t="inlineStr">
         <is>
           <t>Pol (lb/hr)</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <t>Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G244" s="6" t="inlineStr">
+      <c r="G259" s="6" t="inlineStr">
         <is>
           <t>Brix %</t>
         </is>
       </c>
-      <c r="H244" s="6" t="inlineStr">
+      <c r="H259" s="6" t="inlineStr">
         <is>
           <t>Purity %</t>
         </is>
       </c>
-      <c r="I244" s="6" t="inlineStr">
+      <c r="I259" s="6" t="inlineStr">
         <is>
           <t>ft³/hr</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="8" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="8" t="inlineStr">
         <is>
           <t>Massecuite</t>
         </is>
       </c>
-      <c r="B245" s="8" t="inlineStr">
+      <c r="B260" s="8" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C245" s="9" t="n">
+      <c r="C260" s="9" t="n">
         <v>23155.64768866853</v>
       </c>
-      <c r="D245" s="9" t="n">
+      <c r="D260" s="9" t="n">
         <v>22113.64354267845</v>
       </c>
-      <c r="E245" s="9" t="n">
+      <c r="E260" s="9" t="n">
         <v>13001.31115930984</v>
       </c>
-      <c r="F245" s="9" t="n">
+      <c r="F260" s="9" t="n">
         <v>1042.004145990086</v>
       </c>
-      <c r="G245" s="10" t="n">
+      <c r="G260" s="10" t="n">
         <v>95.5</v>
       </c>
-      <c r="H245" s="10" t="n">
+      <c r="H260" s="10" t="n">
         <v>58.79316601182356</v>
       </c>
-      <c r="I245" s="9" t="n">
+      <c r="I260" s="9" t="n">
         <v>244.3357752720343</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="12" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="12" t="inlineStr">
         <is>
           <t>Wash Water</t>
         </is>
       </c>
-      <c r="B246" s="12" t="inlineStr">
+      <c r="B261" s="12" t="inlineStr">
         <is>
           <t>In</t>
         </is>
       </c>
-      <c r="C246" s="13" t="n">
+      <c r="C261" s="13" t="n">
         <v>1768.815522394303</v>
       </c>
-      <c r="D246" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E246" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F246" s="13" t="n">
+      <c r="D261" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" s="13" t="n">
         <v>1768.815522394303</v>
       </c>
-      <c r="G246" s="12" t="inlineStr"/>
-      <c r="H246" s="12" t="inlineStr"/>
-      <c r="I246" s="12" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="8" t="inlineStr">
+      <c r="G261" s="12" t="inlineStr"/>
+      <c r="H261" s="12" t="inlineStr"/>
+      <c r="I261" s="12" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
         <is>
           <t>Sugar Out</t>
         </is>
       </c>
-      <c r="B247" s="8" t="inlineStr">
+      <c r="B262" s="8" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C247" s="9" t="n">
+      <c r="C262" s="9" t="n">
         <v>12889.10545851479</v>
       </c>
-      <c r="D247" s="9" t="n">
+      <c r="D262" s="9" t="n">
         <v>12244.65018558905</v>
       </c>
-      <c r="E247" s="9" t="n">
+      <c r="E262" s="9" t="n">
         <v>10040.61315218302</v>
       </c>
-      <c r="F247" s="9" t="n">
+      <c r="F262" s="9" t="n">
         <v>644.4552729257393</v>
       </c>
-      <c r="G247" s="10" t="n">
+      <c r="G262" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="H247" s="10" t="n">
+      <c r="H262" s="10" t="n">
         <v>82</v>
       </c>
-      <c r="I247" s="9" t="n">
+      <c r="I262" s="9" t="n">
         <v>136.3276586152765</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="12" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>Molasses Out</t>
         </is>
       </c>
-      <c r="B248" s="12" t="inlineStr">
+      <c r="B263" s="12" t="inlineStr">
         <is>
           <t>Out</t>
         </is>
       </c>
-      <c r="C248" s="13" t="n">
+      <c r="C263" s="13" t="n">
         <v>12035.35775254805</v>
       </c>
-      <c r="D248" s="13" t="n">
+      <c r="D263" s="13" t="n">
         <v>9868.993357089399</v>
       </c>
-      <c r="E248" s="13" t="n">
+      <c r="E263" s="13" t="n">
         <v>2960.69800712682</v>
       </c>
-      <c r="F248" s="13" t="n">
+      <c r="F263" s="13" t="n">
         <v>2166.36439545865</v>
       </c>
-      <c r="G248" s="14" t="n">
+      <c r="G263" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="H248" s="14" t="n">
+      <c r="H263" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="I248" s="13" t="n">
+      <c r="I263" s="13" t="n">
         <v>135.3817808614094</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="15" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="15" t="inlineStr">
         <is>
           <t>Total In</t>
         </is>
       </c>
-      <c r="B249" s="15" t="inlineStr"/>
-      <c r="C249" s="16" t="n">
+      <c r="B264" s="15" t="inlineStr"/>
+      <c r="C264" s="16" t="n">
         <v>24924.46321106284</v>
       </c>
-      <c r="D249" s="16" t="n">
+      <c r="D264" s="16" t="n">
         <v>22113.64354267845</v>
       </c>
-      <c r="E249" s="16" t="n">
+      <c r="E264" s="16" t="n">
         <v>13001.31115930984</v>
       </c>
-      <c r="F249" s="16" t="n">
+      <c r="F264" s="16" t="n">
         <v>2810.819668384389</v>
       </c>
-      <c r="G249" s="15" t="inlineStr"/>
-      <c r="H249" s="15" t="inlineStr"/>
-      <c r="I249" s="15" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="15" t="inlineStr">
+      <c r="G264" s="15" t="inlineStr"/>
+      <c r="H264" s="15" t="inlineStr"/>
+      <c r="I264" s="15" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="15" t="inlineStr">
         <is>
           <t>Total Out</t>
         </is>
       </c>
-      <c r="B250" s="15" t="inlineStr"/>
-      <c r="C250" s="16" t="n">
+      <c r="B265" s="15" t="inlineStr"/>
+      <c r="C265" s="16" t="n">
         <v>24924.46321106284</v>
       </c>
-      <c r="D250" s="16" t="n">
+      <c r="D265" s="16" t="n">
         <v>22113.64354267845</v>
       </c>
-      <c r="E250" s="16" t="n">
+      <c r="E265" s="16" t="n">
         <v>13001.31115930984</v>
       </c>
-      <c r="F250" s="16" t="n">
+      <c r="F265" s="16" t="n">
         <v>2810.819668384389</v>
       </c>
-      <c r="G250" s="15" t="inlineStr"/>
-      <c r="H250" s="15" t="inlineStr"/>
-      <c r="I250" s="15" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="15" t="inlineStr">
+      <c r="G265" s="15" t="inlineStr"/>
+      <c r="H265" s="15" t="inlineStr"/>
+      <c r="I265" s="15" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="15" t="inlineStr">
         <is>
           <t>Net (In - Out)</t>
         </is>
       </c>
-      <c r="B251" s="15" t="inlineStr"/>
-      <c r="C251" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D251" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E251" s="16" t="n">
+      <c r="B266" s="15" t="inlineStr"/>
+      <c r="C266" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" s="16" t="n">
         <v>-1.818989403545856e-12</v>
       </c>
-      <c r="F251" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" s="15" t="inlineStr"/>
-      <c r="H251" s="15" t="inlineStr"/>
-      <c r="I251" s="15" t="inlineStr"/>
-    </row>
-    <row r="253" ht="17" customHeight="1">
-      <c r="A253" s="4" t="inlineStr">
+      <c r="F266" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="15" t="inlineStr"/>
+      <c r="H266" s="15" t="inlineStr"/>
+      <c r="I266" s="15" t="inlineStr"/>
+    </row>
+    <row r="268" ht="17" customHeight="1">
+      <c r="A268" s="4" t="inlineStr">
         <is>
           <t>PAN VAPOR CONDENSERS  (one per pan)</t>
         </is>
       </c>
-      <c r="B253" s="5" t="n"/>
-      <c r="C253" s="5" t="n"/>
-      <c r="D253" s="5" t="n"/>
-      <c r="E253" s="5" t="n"/>
-      <c r="F253" s="5" t="n"/>
-      <c r="G253" s="5" t="n"/>
-      <c r="H253" s="5" t="n"/>
-      <c r="I253" s="5" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="6" t="inlineStr">
+      <c r="B268" s="5" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="5" t="n"/>
+      <c r="F268" s="5" t="n"/>
+      <c r="G268" s="5" t="n"/>
+      <c r="H268" s="5" t="n"/>
+      <c r="I268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
         <is>
           <t>Condenser</t>
         </is>
       </c>
-      <c r="B254" s="6" t="inlineStr">
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>Vapor (lb/hr)</t>
         </is>
       </c>
-      <c r="C254" s="6" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
         <is>
           <t>Sat T (°F)</t>
         </is>
       </c>
-      <c r="D254" s="6" t="inlineStr">
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>h_fg (BTU/lb)</t>
         </is>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="E269" s="6" t="inlineStr">
         <is>
           <t>Heat (MM BTU/hr)</t>
         </is>
       </c>
-      <c r="F254" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <t>Inj Water (lb/hr)</t>
         </is>
       </c>
-      <c r="G254" s="6" t="inlineStr">
+      <c r="G269" s="6" t="inlineStr">
         <is>
           <t>Inj Water (GPM)</t>
         </is>
       </c>
-      <c r="H254" s="6" t="inlineStr">
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>Water Out (°F)</t>
         </is>
       </c>
-      <c r="I254" s="6" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>Total Out (lb/hr)</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="8" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="8" t="inlineStr">
         <is>
           <t>A1 Pans</t>
         </is>
       </c>
-      <c r="B255" s="9" t="n">
+      <c r="B270" s="9" t="n">
         <v>24253.75993915585</v>
       </c>
-      <c r="C255" s="10" t="n">
+      <c r="C270" s="10" t="n">
         <v>143.355890609762</v>
       </c>
-      <c r="D255" s="10" t="n">
+      <c r="D270" s="10" t="n">
         <v>1011.249247318053</v>
       </c>
-      <c r="E255" s="22" t="n">
+      <c r="E270" s="23" t="n">
         <v>24.52659648310409</v>
       </c>
-      <c r="F255" s="9" t="n">
+      <c r="F270" s="9" t="n">
         <v>459679.2632042904</v>
       </c>
-      <c r="G255" s="9" t="n">
+      <c r="G270" s="9" t="n">
         <v>918.6236275065756</v>
       </c>
-      <c r="H255" s="10" t="n">
+      <c r="H270" s="10" t="n">
         <v>143.355890609762</v>
       </c>
-      <c r="I255" s="9" t="n">
+      <c r="I270" s="9" t="n">
         <v>483933.0231434462</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="12" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="12" t="inlineStr">
         <is>
           <t>A2 Pans</t>
         </is>
       </c>
-      <c r="B256" s="13" t="n">
+      <c r="B271" s="13" t="n">
         <v>13576.91053948484</v>
       </c>
-      <c r="C256" s="14" t="n">
+      <c r="C271" s="14" t="n">
         <v>143.355890609762</v>
       </c>
-      <c r="D256" s="14" t="n">
+      <c r="D271" s="14" t="n">
         <v>1011.249247318053</v>
       </c>
-      <c r="E256" s="23" t="n">
+      <c r="E271" s="24" t="n">
         <v>13.72964056395858</v>
       </c>
-      <c r="F256" s="13" t="n">
+      <c r="F271" s="13" t="n">
         <v>257321.9265399464</v>
       </c>
-      <c r="G256" s="13" t="n">
+      <c r="G271" s="13" t="n">
         <v>514.2324671062078</v>
       </c>
-      <c r="H256" s="14" t="n">
+      <c r="H271" s="14" t="n">
         <v>143.355890609762</v>
       </c>
-      <c r="I256" s="13" t="n">
+      <c r="I271" s="13" t="n">
         <v>270898.8370794312</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="8" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="8" t="inlineStr">
         <is>
           <t>B Pans</t>
         </is>
       </c>
-      <c r="B257" s="9" t="n">
+      <c r="B272" s="9" t="n">
         <v>10741.66285121619</v>
       </c>
-      <c r="C257" s="10" t="n">
+      <c r="C272" s="10" t="n">
         <v>133.0828737186033</v>
       </c>
-      <c r="D257" s="10" t="n">
+      <c r="D272" s="10" t="n">
         <v>1017.228576695272</v>
       </c>
-      <c r="E257" s="22" t="n">
+      <c r="E272" s="23" t="n">
         <v>10.92672641348312</v>
       </c>
-      <c r="F257" s="9" t="n">
+      <c r="F272" s="9" t="n">
         <v>253621.1136901234</v>
       </c>
-      <c r="G257" s="9" t="n">
+      <c r="G272" s="9" t="n">
         <v>506.8367579738678</v>
       </c>
-      <c r="H257" s="10" t="n">
+      <c r="H272" s="10" t="n">
         <v>133.0828737186033</v>
       </c>
-      <c r="I257" s="9" t="n">
+      <c r="I272" s="9" t="n">
         <v>264362.7765413396</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="12" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="12" t="inlineStr">
         <is>
           <t>Grain Pans</t>
         </is>
       </c>
-      <c r="B258" s="13" t="n">
+      <c r="B273" s="13" t="n">
         <v>2186.750452105832</v>
       </c>
-      <c r="C258" s="14" t="n">
+      <c r="C273" s="14" t="n">
         <v>129.059477265374</v>
       </c>
-      <c r="D258" s="14" t="n">
+      <c r="D273" s="14" t="n">
         <v>1019.563890979194</v>
       </c>
-      <c r="E258" s="23" t="n">
+      <c r="E273" s="24" t="n">
         <v>2.229531799549534</v>
       </c>
-      <c r="F258" s="13" t="n">
+      <c r="F273" s="13" t="n">
         <v>57080.43106675161</v>
       </c>
-      <c r="G258" s="13" t="n">
+      <c r="G273" s="13" t="n">
         <v>114.0696064483446</v>
       </c>
-      <c r="H258" s="14" t="n">
+      <c r="H273" s="14" t="n">
         <v>129.059477265374</v>
       </c>
-      <c r="I258" s="13" t="n">
+      <c r="I273" s="13" t="n">
         <v>59267.18151885744</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="8" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="8" t="inlineStr">
         <is>
           <t>C Pans</t>
         </is>
       </c>
-      <c r="B259" s="9" t="n">
+      <c r="B274" s="9" t="n">
         <v>6642.056640547988</v>
       </c>
-      <c r="C259" s="10" t="n">
+      <c r="C274" s="10" t="n">
         <v>119.6832047961655</v>
       </c>
-      <c r="D259" s="10" t="n">
+      <c r="D274" s="10" t="n">
         <v>1024.996584701115</v>
       </c>
-      <c r="E259" s="22" t="n">
+      <c r="E274" s="23" t="n">
         <v>6.80808537195305</v>
       </c>
-      <c r="F259" s="9" t="n">
+      <c r="F274" s="9" t="n">
         <v>229358.1646154506</v>
       </c>
-      <c r="G259" s="9" t="n">
+      <c r="G274" s="9" t="n">
         <v>458.3496495112922</v>
       </c>
-      <c r="H259" s="10" t="n">
+      <c r="H274" s="10" t="n">
         <v>119.6832047961655</v>
       </c>
-      <c r="I259" s="9" t="n">
+      <c r="I274" s="9" t="n">
         <v>236000.2212559986</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="15" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B260" s="16" t="n">
+      <c r="B275" s="16" t="n">
         <v>57401.1404225107</v>
       </c>
-      <c r="C260" s="15" t="inlineStr"/>
-      <c r="D260" s="15" t="inlineStr"/>
-      <c r="E260" s="24" t="n">
+      <c r="C275" s="15" t="inlineStr"/>
+      <c r="D275" s="15" t="inlineStr"/>
+      <c r="E275" s="25" t="n">
         <v>58.22058063204837</v>
       </c>
-      <c r="F260" s="16" t="n">
+      <c r="F275" s="16" t="n">
         <v>1257060.899116562</v>
       </c>
-      <c r="G260" s="16" t="n">
+      <c r="G275" s="16" t="n">
         <v>2512.112108546288</v>
       </c>
-      <c r="H260" s="15" t="inlineStr"/>
-      <c r="I260" s="16" t="n">
+      <c r="H275" s="15" t="inlineStr"/>
+      <c r="I275" s="16" t="n">
         <v>1314462.039539073</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="17" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="17" t="inlineStr">
         <is>
           <t>Injection water supply temp</t>
         </is>
       </c>
-      <c r="B261" s="25" t="n">
+      <c r="B276" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="C261" s="19" t="inlineStr">
+      <c r="C276" s="19" t="inlineStr">
         <is>
           <t>°F</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="17" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="17" t="inlineStr">
         <is>
           <t>Note: if using CoolingTowerSystem, ignore these injection water demands - they are re-solved there at the delivered water temp.</t>
         </is>
       </c>
-      <c r="B262" s="20" t="inlineStr"/>
+      <c r="B277" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A243:I243"/>
-    <mergeCell ref="A164:I164"/>
+    <mergeCell ref="A227:I227"/>
+    <mergeCell ref="A212:I212"/>
+    <mergeCell ref="A137:I137"/>
+    <mergeCell ref="A193:I193"/>
+    <mergeCell ref="A268:I268"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A154:I154"/>
     <mergeCell ref="A101:I101"/>
+    <mergeCell ref="A179:I179"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A160:I160"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A194:I194"/>
     <mergeCell ref="A203:I203"/>
-    <mergeCell ref="A234:I234"/>
-    <mergeCell ref="A215:I215"/>
-    <mergeCell ref="A184:I184"/>
-    <mergeCell ref="A253:I253"/>
-    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A240:I240"/>
+    <mergeCell ref="A170:I170"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A173:I173"/>
+    <mergeCell ref="A258:I258"/>
+    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="A249:I249"/>
     <mergeCell ref="A114:I114"/>
-    <mergeCell ref="A143:I143"/>
-    <mergeCell ref="A225:I225"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="A146:I146"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
